--- a/output/pdf_financials_xlsx/SPX.xlsx
+++ b/output/pdf_financials_xlsx/SPX.xlsx
@@ -2708,25 +2708,25 @@
         <v>0.038474</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.120681</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004581</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.708378</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.737201</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.059291</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.026625</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.665665</v>
       </c>
     </row>
     <row r="35">
@@ -2846,25 +2846,25 @@
         <v>0.038474</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.120681</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.004581</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.468</v>
+        <v>2.176378</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.468</v>
+        <v>1.205201</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.30149</v>
+        <v>0.360781</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.17228</v>
+        <v>0.198905</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.107675</v>
+        <v>0.77334</v>
       </c>
     </row>
     <row r="37">
@@ -3674,25 +3674,25 @@
         <v>0.070463</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.139747</v>
+        <v>0.019066</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.409893</v>
+        <v>0.405312</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.263932</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.456805</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.06865499999999999</v>
+        <v>0.009364000000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.027905</v>
+        <v>0.00128</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.746664</v>
+        <v>0.080999</v>
       </c>
     </row>
     <row r="49">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -14286,7 +14286,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
